--- a/data_lake/datos_diarios_preliminares/dt=2026-07-29/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-29/temperaturamed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5B64C2-3E4E-40AF-9265-CE2F16615416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEB6582-8ADF-469A-97B0-9FCF0C84C932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AF$1:$AF$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AL$1:$AL$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -103,7 +103,7 @@
     <t>Aeropuerto Sesquicentenario</t>
   </si>
   <si>
-    <t>Met_Aeronautica</t>
+    <t>Grupo Observación y Monitoreo</t>
   </si>
   <si>
     <t>Archipiélago de San Andres, Providencia y Santa Catalina</t>
@@ -6341,7 +6341,7 @@
   <cols>
     <col min="1" max="1" width="16.7109375" style="97" customWidth="1"/>
     <col min="2" max="2" width="36.28515625" style="50" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="50" customWidth="1"/>
+    <col min="3" max="3" width="59.42578125" style="50" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.140625" style="50" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" style="50" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="50" customWidth="1"/>
@@ -6354,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="114" width="32.42578125" style="50" customWidth="1"/>
-    <col min="115" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="115" width="32.42578125" style="50" customWidth="1"/>
+    <col min="116" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6719,17 +6719,19 @@
       <c r="AK5" s="56">
         <v>29.1</v>
       </c>
-      <c r="AL5" s="56"/>
+      <c r="AL5" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AM5" s="56"/>
       <c r="AN5" s="56"/>
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.840740740740738</v>
+        <v>28.796428571428571</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6737,7 +6739,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.68752585176946823</v>
+        <v>0.64321368245730071</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6852,17 +6854,19 @@
       <c r="AK6" s="56">
         <v>29.1</v>
       </c>
-      <c r="AL6" s="56"/>
+      <c r="AL6" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AM6" s="56"/>
       <c r="AN6" s="56"/>
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.851851851851851</v>
+        <v>28.807142857142857</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6870,7 +6874,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.45661796290303158</v>
+        <v>0.41190896819403733</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6985,17 +6989,19 @@
       <c r="AK7" s="56">
         <v>30.5</v>
       </c>
-      <c r="AL7" s="56"/>
+      <c r="AL7" s="56">
+        <v>30.9</v>
+      </c>
       <c r="AM7" s="56"/>
       <c r="AN7" s="56"/>
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.411111111111111</v>
+        <v>31.392857142857142</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7003,7 +7009,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.210930619559651</v>
+        <v>2.1926766513056819</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7118,17 +7124,19 @@
       <c r="AK8" s="56">
         <v>28.7</v>
       </c>
-      <c r="AL8" s="56"/>
+      <c r="AL8" s="56">
+        <v>30.3</v>
+      </c>
       <c r="AM8" s="56"/>
       <c r="AN8" s="56"/>
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.662962962962965</v>
+        <v>29.685714285714287</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7136,7 +7144,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.0844236467915636</v>
+        <v>1.1071749695428856</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7251,17 +7259,19 @@
       <c r="AK9" s="56">
         <v>28.1</v>
       </c>
-      <c r="AL9" s="56"/>
+      <c r="AL9" s="56">
+        <v>30.8</v>
+      </c>
       <c r="AM9" s="56"/>
       <c r="AN9" s="56"/>
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.318518518518523</v>
+        <v>29.371428571428574</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7269,7 +7279,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.46895046411170682</v>
+        <v>-0.41604041120165647</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7384,17 +7394,19 @@
       <c r="AK10" s="56">
         <v>29.3</v>
       </c>
-      <c r="AL10" s="56"/>
+      <c r="AL10" s="56">
+        <v>31.5</v>
+      </c>
       <c r="AM10" s="56"/>
       <c r="AN10" s="56"/>
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.585185185185182</v>
+        <v>31.582142857142856</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7402,7 +7414,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.5057631507801226</v>
+        <v>1.5027208227377962</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7517,17 +7529,19 @@
       <c r="AK11" s="56">
         <v>31.1</v>
       </c>
-      <c r="AL11" s="56"/>
+      <c r="AL11" s="56">
+        <v>33.5</v>
+      </c>
       <c r="AM11" s="56"/>
       <c r="AN11" s="56"/>
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.529629629629632</v>
+        <v>32.564285714285717</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7535,7 +7549,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>2.5257155524017811</v>
+        <v>2.560371637057866</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7650,17 +7664,19 @@
       <c r="AK12" s="56">
         <v>28.3</v>
       </c>
-      <c r="AL12" s="56"/>
+      <c r="AL12" s="56">
+        <v>30.1</v>
+      </c>
       <c r="AM12" s="56"/>
       <c r="AN12" s="56"/>
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>29.981481481481474</v>
+        <v>29.985714285714277</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7668,7 +7684,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7158150921658937</v>
+        <v>1.7200478963986967</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7783,17 +7799,19 @@
       <c r="AK13" s="56">
         <v>29.3</v>
       </c>
-      <c r="AL13" s="56"/>
+      <c r="AL13" s="56">
+        <v>31.2</v>
+      </c>
       <c r="AM13" s="56"/>
       <c r="AN13" s="56"/>
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>29.896296296296288</v>
+        <v>29.94285714285714</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7801,7 +7819,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.566901598483927</v>
+        <v>1.6134624450447781</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7916,17 +7934,19 @@
       <c r="AK14" s="56">
         <v>23.2</v>
       </c>
-      <c r="AL14" s="56"/>
+      <c r="AL14" s="56">
+        <v>24.5</v>
+      </c>
       <c r="AM14" s="56"/>
       <c r="AN14" s="56"/>
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.585185185185182</v>
+        <v>23.61785714285714</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7934,7 +7954,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.8636451612903322</v>
+        <v>1.8963171189622905</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8049,17 +8069,19 @@
       <c r="AK15" s="56">
         <v>29</v>
       </c>
-      <c r="AL15" s="56"/>
+      <c r="AL15" s="56">
+        <v>31.4</v>
+      </c>
       <c r="AM15" s="56"/>
       <c r="AN15" s="56"/>
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.18148148148148</v>
+        <v>29.260714285714283</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8067,7 +8089,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>0.94597610513740094</v>
+        <v>1.0252089093702033</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8182,17 +8204,19 @@
       <c r="AK16" s="56">
         <v>28.7</v>
       </c>
-      <c r="AL16" s="56"/>
+      <c r="AL16" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AM16" s="56"/>
       <c r="AN16" s="56"/>
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.359259259259261</v>
+        <v>28.371428571428574</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8200,7 +8224,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.72160641085628185</v>
+        <v>0.73377572302559457</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8315,17 +8339,19 @@
       <c r="AK17" s="56">
         <v>23.6</v>
       </c>
-      <c r="AL17" s="56"/>
+      <c r="AL17" s="56">
+        <v>25.7</v>
+      </c>
       <c r="AM17" s="56"/>
       <c r="AN17" s="56"/>
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.592592592592595</v>
+        <v>24.632142857142863</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8333,7 +8359,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.60896892343639664</v>
+        <v>0.64851918798666475</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8448,17 +8474,19 @@
       <c r="AK18" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="AL18" s="56"/>
+      <c r="AL18" s="56">
+        <v>19.3</v>
+      </c>
       <c r="AM18" s="56"/>
       <c r="AN18" s="56"/>
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.751851851851853</v>
+        <v>18.771428571428572</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8466,7 +8494,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.3335005973715717</v>
+        <v>1.3530773169482906</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8581,17 +8609,19 @@
       <c r="AK19" s="56">
         <v>23</v>
       </c>
-      <c r="AL19" s="56"/>
+      <c r="AL19" s="56">
+        <v>25.5</v>
+      </c>
       <c r="AM19" s="56"/>
       <c r="AN19" s="56"/>
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.18148148148148</v>
+        <v>24.228571428571428</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8599,7 +8629,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.0479465352449289</v>
+        <v>2.0950364823348764</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8714,17 +8744,19 @@
       <c r="AK20" s="56">
         <v>23.8</v>
       </c>
-      <c r="AL20" s="56"/>
+      <c r="AL20" s="56">
+        <v>25.8</v>
+      </c>
       <c r="AM20" s="56"/>
       <c r="AN20" s="56"/>
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.240740740740737</v>
+        <v>24.296428571428567</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8732,7 +8764,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.6330753147688668</v>
+        <v>1.6887631454566971</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8847,17 +8879,19 @@
       <c r="AK21" s="56">
         <v>27.1</v>
       </c>
-      <c r="AL21" s="56"/>
+      <c r="AL21" s="56">
+        <v>28.1</v>
+      </c>
       <c r="AM21" s="56"/>
       <c r="AN21" s="56"/>
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.12222222222222</v>
+        <v>27.157142857142855</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8865,7 +8899,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.4321403304650886</v>
+        <v>2.4670609653857234</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8980,17 +9014,19 @@
       <c r="AK22" s="56">
         <v>15.3</v>
       </c>
-      <c r="AL22" s="56"/>
+      <c r="AL22" s="56">
+        <v>15.5</v>
+      </c>
       <c r="AM22" s="56"/>
       <c r="AN22" s="56"/>
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.481481481481481</v>
+        <v>15.482142857142858</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8998,7 +9034,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.7011485617130813</v>
+        <v>1.701809937374458</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9113,17 +9149,19 @@
       <c r="AK23" s="56">
         <v>25.2</v>
       </c>
-      <c r="AL23" s="56"/>
+      <c r="AL23" s="56">
+        <v>26.5</v>
+      </c>
       <c r="AM23" s="56"/>
       <c r="AN23" s="56"/>
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.059259259259257</v>
+        <v>26.074999999999996</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9246,17 +9284,19 @@
       <c r="AK24" s="56">
         <v>29.3</v>
       </c>
-      <c r="AL24" s="56"/>
+      <c r="AL24" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AM24" s="56"/>
       <c r="AN24" s="56"/>
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.400000000000002</v>
+        <v>29.442857142857147</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9264,7 +9304,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.037641515263882</v>
+        <v>1.0804986581210265</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9379,17 +9419,19 @@
       <c r="AK25" s="56">
         <v>21.2</v>
       </c>
-      <c r="AL25" s="56"/>
+      <c r="AL25" s="56">
+        <v>22.1</v>
+      </c>
       <c r="AM25" s="56"/>
       <c r="AN25" s="56"/>
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>21.840740740740738</v>
+        <v>21.849999999999998</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9397,7 +9439,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.9073162845385383</v>
+        <v>1.9165755437977978</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9512,17 +9554,19 @@
       <c r="AK26" s="56">
         <v>10.4</v>
       </c>
-      <c r="AL26" s="56"/>
+      <c r="AL26" s="56">
+        <v>11.1</v>
+      </c>
       <c r="AM26" s="56"/>
       <c r="AN26" s="56"/>
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.53333333333333</v>
+        <v>11.517857142857141</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9530,7 +9574,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.1630184331797402</v>
+        <v>1.1475422427035511</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9645,17 +9689,19 @@
       <c r="AK27" s="56">
         <v>28.1</v>
       </c>
-      <c r="AL27" s="56"/>
+      <c r="AL27" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AM27" s="56"/>
       <c r="AN27" s="56"/>
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.040740740740745</v>
+        <v>28.078571428571433</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9663,7 +9709,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.0520347711448963</v>
+        <v>1.0898654589755843</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9778,17 +9824,19 @@
       <c r="AK28" s="56">
         <v>27.1</v>
       </c>
-      <c r="AL28" s="56"/>
+      <c r="AL28" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AM28" s="56"/>
       <c r="AN28" s="56"/>
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.511111111111113</v>
+        <v>26.596428571428572</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9796,7 +9844,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.75969255963417126</v>
+        <v>0.84501001995162994</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9911,17 +9959,19 @@
       <c r="AK29" s="56">
         <v>28.6</v>
       </c>
-      <c r="AL29" s="56"/>
+      <c r="AL29" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AM29" s="56"/>
       <c r="AN29" s="56"/>
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.714814814814819</v>
+        <v>27.75714285714286</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9929,7 +9979,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.76077260055757989</v>
+        <v>0.80310064288562089</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10044,17 +10094,19 @@
       <c r="AK30" s="56">
         <v>25.7</v>
       </c>
-      <c r="AL30" s="56"/>
+      <c r="AL30" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AM30" s="56"/>
       <c r="AN30" s="56"/>
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.3</v>
+        <v>25.357142857142858</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10062,7 +10114,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.7819985168706296</v>
+        <v>0.83914137401348654</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -10177,17 +10229,19 @@
       <c r="AK31" s="98">
         <v>26.2</v>
       </c>
-      <c r="AL31" s="98"/>
+      <c r="AL31" s="98">
+        <v>27.4</v>
+      </c>
       <c r="AM31" s="98"/>
       <c r="AN31" s="98"/>
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.781481481481482</v>
+        <v>26.803571428571427</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10195,7 +10249,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4125328554360834</v>
+        <v>1.4346228025260288</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10310,17 +10364,19 @@
       <c r="AK32" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="AL32" s="56"/>
+      <c r="AL32" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AM32" s="56"/>
       <c r="AN32" s="56"/>
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.458024691358023</v>
+        <v>20.448809523809526</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10328,7 +10384,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.8011686392491839</v>
+        <v>2.7919534717006869</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10443,17 +10499,19 @@
       <c r="AK33" s="56">
         <v>28.05</v>
       </c>
-      <c r="AL33" s="56"/>
+      <c r="AL33" s="56">
+        <v>28.65</v>
+      </c>
       <c r="AM33" s="56"/>
       <c r="AN33" s="56"/>
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>27.907407407407412</v>
+        <v>27.933928571428574</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10461,7 +10519,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.0799353261948603</v>
+        <v>1.1064564902160221</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10576,17 +10634,19 @@
       <c r="AK34" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="AL34" s="56"/>
+      <c r="AL34" s="56">
+        <v>21.6</v>
+      </c>
       <c r="AM34" s="56"/>
       <c r="AN34" s="56"/>
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.281481481481482</v>
+        <v>21.292857142857144</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10594,7 +10654,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.4942838898011601</v>
+        <v>1.5056595511768229</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10709,17 +10769,19 @@
       <c r="AK35" s="56">
         <v>23.9</v>
       </c>
-      <c r="AL35" s="56"/>
+      <c r="AL35" s="56">
+        <v>24.8</v>
+      </c>
       <c r="AM35" s="56"/>
       <c r="AN35" s="56"/>
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.524074074074072</v>
+        <v>24.533928571428568</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10727,7 +10789,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.48582617435667075</v>
+        <v>0.49568067171116681</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10842,17 +10904,19 @@
       <c r="AK36" s="56">
         <v>19.649999999999999</v>
       </c>
-      <c r="AL36" s="56"/>
+      <c r="AL36" s="56">
+        <v>19.7</v>
+      </c>
       <c r="AM36" s="56"/>
       <c r="AN36" s="56"/>
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>19.987037037037037</v>
+        <v>19.976785714285715</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10860,7 +10924,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>0.98822597381864696</v>
+        <v>0.97797465106732417</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10975,17 +11039,19 @@
       <c r="AK37" s="56">
         <v>27.3</v>
       </c>
-      <c r="AL37" s="56"/>
+      <c r="AL37" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AM37" s="56"/>
       <c r="AN37" s="56"/>
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.36851851851852</v>
+        <v>27.369642857142857</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10993,7 +11059,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.4822886445811392</v>
+        <v>1.4834129832054757</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11104,17 +11170,19 @@
       <c r="AK38" s="56">
         <v>15.05</v>
       </c>
-      <c r="AL38" s="56"/>
+      <c r="AL38" s="56">
+        <v>15.55</v>
+      </c>
       <c r="AM38" s="56"/>
       <c r="AN38" s="56"/>
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>15.903999999999998</v>
+        <v>15.890384615384615</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11122,7 +11190,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>0.88607099304931758</v>
+        <v>0.87245560843393477</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11356,17 +11424,19 @@
       <c r="AK40" s="56">
         <v>24.733333333333331</v>
       </c>
-      <c r="AL40" s="56"/>
+      <c r="AL40" s="56">
+        <v>25.13333333333334</v>
+      </c>
       <c r="AM40" s="56"/>
       <c r="AN40" s="56"/>
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.194444444444439</v>
+        <v>25.191666666666663</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11374,7 +11444,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.342653696017468</v>
+        <v>2.3398759182396915</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11487,17 +11557,19 @@
       <c r="AK41" s="56">
         <v>18.86666666666666</v>
       </c>
-      <c r="AL41" s="56"/>
+      <c r="AL41" s="56">
+        <v>19</v>
+      </c>
       <c r="AM41" s="56"/>
       <c r="AN41" s="56"/>
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.09871794871794</v>
+        <v>20.058024691358018</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11505,7 +11577,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>1.6066087573902017</v>
+        <v>1.5659155000302789</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11620,17 +11692,19 @@
       <c r="AK42" s="56">
         <v>26.9</v>
       </c>
-      <c r="AL42" s="56"/>
+      <c r="AL42" s="56">
+        <v>27.65</v>
+      </c>
       <c r="AM42" s="56"/>
       <c r="AN42" s="56"/>
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.947222222222219</v>
+        <v>27.936607142857138</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11638,7 +11712,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.19453670516394794</v>
+        <v>0.18392162579886673</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11749,17 +11823,19 @@
       <c r="AK43" s="56">
         <v>28.15</v>
       </c>
-      <c r="AL43" s="56"/>
+      <c r="AL43" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AM43" s="56"/>
       <c r="AN43" s="56"/>
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.274000000000004</v>
+        <v>29.25961538461539</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11882,17 +11958,19 @@
       <c r="AK44" s="56">
         <v>27.875</v>
       </c>
-      <c r="AL44" s="56"/>
+      <c r="AL44" s="56">
+        <v>28.75</v>
+      </c>
       <c r="AM44" s="56"/>
       <c r="AN44" s="56"/>
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.5037037037037</v>
+        <v>28.512499999999996</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11900,7 +11978,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.1613602594208778</v>
+        <v>1.170156555717174</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12015,17 +12093,19 @@
       <c r="AK45" s="56">
         <v>27.2</v>
       </c>
-      <c r="AL45" s="56"/>
+      <c r="AL45" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AM45" s="56"/>
       <c r="AN45" s="56"/>
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.164814814814822</v>
+        <v>29.166071428571435</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12033,7 +12113,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.3967073398833918</v>
+        <v>1.397963953640005</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12148,17 +12228,19 @@
       <c r="AK46" s="56">
         <v>27.7</v>
       </c>
-      <c r="AL46" s="56"/>
+      <c r="AL46" s="56">
+        <v>28.75</v>
+      </c>
       <c r="AM46" s="56"/>
       <c r="AN46" s="56"/>
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>28.88425925925926</v>
+        <v>28.879464285714285</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12166,7 +12248,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>0.97806162736177882</v>
+        <v>0.97326665381680399</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12281,17 +12363,19 @@
       <c r="AK47" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="AL47" s="56"/>
+      <c r="AL47" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AM47" s="56"/>
       <c r="AN47" s="56"/>
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ47" s="71">
         <f t="shared" si="1"/>
-        <v>29.867901234567906</v>
+        <v>29.894047619047626</v>
       </c>
       <c r="AR47" s="71">
         <f>IFERROR(VLOOKUP(A47,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12299,7 +12383,7 @@
       </c>
       <c r="AS47" s="71">
         <f t="shared" si="2"/>
-        <v>1.8990253752505168</v>
+        <v>1.9251717597302367</v>
       </c>
     </row>
     <row r="48" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12572,17 +12656,19 @@
       <c r="AK50" s="56">
         <v>28.4</v>
       </c>
-      <c r="AL50" s="56"/>
+      <c r="AL50" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AM50" s="56"/>
       <c r="AN50" s="56"/>
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>29.18333333333333</v>
+        <v>29.205357142857139</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12590,7 +12676,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>1.8946429873015092</v>
+        <v>1.9166667968253179</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12891,17 +12977,19 @@
       <c r="AK53" s="56">
         <v>27</v>
       </c>
-      <c r="AL53" s="56"/>
+      <c r="AL53" s="56">
+        <v>29</v>
+      </c>
       <c r="AM53" s="56"/>
       <c r="AN53" s="56"/>
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>28.816666666666666</v>
+        <v>28.823214285714283</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12909,7 +12997,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.4574203700761181</v>
+        <v>1.4639679891237343</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13024,17 +13112,19 @@
       <c r="AK54" s="56">
         <v>28.7</v>
       </c>
-      <c r="AL54" s="56"/>
+      <c r="AL54" s="56">
+        <v>29.85</v>
+      </c>
       <c r="AM54" s="56"/>
       <c r="AN54" s="56"/>
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>29.981481481481492</v>
+        <v>29.976785714285722</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13042,7 +13132,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.4832554564150726</v>
+        <v>1.4785596892193027</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13143,17 +13233,19 @@
       <c r="AK55" s="56">
         <v>27.2</v>
       </c>
-      <c r="AL55" s="56"/>
+      <c r="AL55" s="56">
+        <v>30.7</v>
+      </c>
       <c r="AM55" s="56"/>
       <c r="AN55" s="56"/>
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v>30.142500000000005</v>
+        <v>30.169047619047628</v>
       </c>
       <c r="AR55" s="71">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13161,7 +13253,7 @@
       </c>
       <c r="AS55" s="71">
         <f t="shared" si="2"/>
-        <v>1.7115403297629648</v>
+        <v>1.7380879488105876</v>
       </c>
     </row>
     <row r="56" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13276,17 +13368,19 @@
       <c r="AK56" s="56">
         <v>27.45</v>
       </c>
-      <c r="AL56" s="56"/>
+      <c r="AL56" s="56">
+        <v>28.65</v>
+      </c>
       <c r="AM56" s="56"/>
       <c r="AN56" s="56"/>
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ56" s="71">
         <f t="shared" si="1"/>
-        <v>29.312962962962963</v>
+        <v>29.289285714285715</v>
       </c>
       <c r="AR56" s="71" t="str">
         <f>IFERROR(VLOOKUP(A56,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13565,17 +13659,19 @@
       <c r="AK59" s="56">
         <v>27.6</v>
       </c>
-      <c r="AL59" s="56"/>
+      <c r="AL59" s="56">
+        <v>30</v>
+      </c>
       <c r="AM59" s="56"/>
       <c r="AN59" s="56"/>
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>29.004807692307693</v>
+        <v>29.041666666666668</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13583,7 +13679,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>0.89058786322553374</v>
+        <v>0.92744683758450819</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13688,17 +13784,19 @@
       <c r="AK60" s="56">
         <v>25.95</v>
       </c>
-      <c r="AL60" s="56"/>
+      <c r="AL60" s="56">
+        <v>26.25</v>
+      </c>
       <c r="AM60" s="56"/>
       <c r="AN60" s="56"/>
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ60" s="71">
         <f t="shared" si="1"/>
-        <v>25.731818181818184</v>
+        <v>25.754347826086956</v>
       </c>
       <c r="AR60" s="71">
         <f>IFERROR(VLOOKUP(A60,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13706,7 +13804,7 @@
       </c>
       <c r="AS60" s="71">
         <f t="shared" si="2"/>
-        <v>1.5872539668698558</v>
+        <v>1.6097836111386279</v>
       </c>
     </row>
     <row r="61" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13821,17 +13919,19 @@
       <c r="AK61" s="56">
         <v>27.2</v>
       </c>
-      <c r="AL61" s="56"/>
+      <c r="AL61" s="56">
+        <v>28.25</v>
+      </c>
       <c r="AM61" s="56"/>
       <c r="AN61" s="56"/>
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>26.696296296296303</v>
+        <v>26.75178571428572</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13839,7 +13939,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>0.98962461457034223</v>
+        <v>1.0451140325597592</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13954,17 +14054,19 @@
       <c r="AK62" s="56">
         <v>26.6</v>
       </c>
-      <c r="AL62" s="56"/>
+      <c r="AL62" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AM62" s="56"/>
       <c r="AN62" s="56"/>
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>25.95802469135803</v>
+        <v>26.045238095238098</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13972,7 +14074,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.4190207513941395</v>
+        <v>1.5062341552742069</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14227,17 +14329,19 @@
       <c r="AK65" s="56">
         <v>25.7</v>
       </c>
-      <c r="AL65" s="56"/>
+      <c r="AL65" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AM65" s="56"/>
       <c r="AN65" s="56"/>
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>25.738888888888894</v>
+        <v>25.757894736842111</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14245,7 +14349,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.7336829305777357</v>
+        <v>0.75268877853095262</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14360,17 +14464,19 @@
       <c r="AK66" s="56">
         <v>26.95</v>
       </c>
-      <c r="AL66" s="56"/>
+      <c r="AL66" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AM66" s="56"/>
       <c r="AN66" s="56"/>
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.690740740740736</v>
+        <v>25.74821428571428</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14378,7 +14484,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.78162591046174512</v>
+        <v>0.83909945543528863</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14489,17 +14595,19 @@
       <c r="AK67" s="56">
         <v>28.15</v>
       </c>
-      <c r="AL67" s="56"/>
+      <c r="AL67" s="56">
+        <v>27.65</v>
+      </c>
       <c r="AM67" s="56"/>
       <c r="AN67" s="56"/>
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.537999999999997</v>
+        <v>25.619230769230764</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14507,7 +14615,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.88679308816878688</v>
+        <v>0.96802385739955454</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14622,17 +14730,19 @@
       <c r="AK68" s="56">
         <v>26.25</v>
       </c>
-      <c r="AL68" s="56"/>
+      <c r="AL68" s="56">
+        <v>27.15</v>
+      </c>
       <c r="AM68" s="56"/>
       <c r="AN68" s="56"/>
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.533333333333331</v>
+        <v>25.591071428571428</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14640,7 +14750,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>1.0082458305903117</v>
+        <v>1.0659839258284087</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14755,17 +14865,19 @@
       <c r="AK69" s="56">
         <v>25.25</v>
       </c>
-      <c r="AL69" s="56"/>
+      <c r="AL69" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AM69" s="56"/>
       <c r="AN69" s="56"/>
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>24.962037037037042</v>
+        <v>24.997321428571436</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14773,7 +14885,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.63963935040503372</v>
+        <v>0.67492374193942695</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14874,17 +14986,19 @@
       <c r="AK70" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="AL70" s="56"/>
+      <c r="AL70" s="56">
+        <v>28</v>
+      </c>
       <c r="AM70" s="56"/>
       <c r="AN70" s="56"/>
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>26.505000000000003</v>
+        <v>26.576190476190476</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14892,7 +15006,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>0.93504130895680149</v>
+        <v>1.0062317851472748</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15007,17 +15121,19 @@
       <c r="AK71" s="56">
         <v>26.4</v>
       </c>
-      <c r="AL71" s="56"/>
+      <c r="AL71" s="56">
+        <v>27.5</v>
+      </c>
       <c r="AM71" s="56"/>
       <c r="AN71" s="56"/>
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.925925925925927</v>
+        <v>25.982142857142858</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15025,7 +15141,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.26348301227239901</v>
+        <v>0.31969994348932929</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15138,17 +15254,19 @@
       <c r="AK72" s="56">
         <v>24.06666666666667</v>
       </c>
-      <c r="AL72" s="56"/>
+      <c r="AL72" s="56">
+        <v>24.166666666666671</v>
+      </c>
       <c r="AM72" s="56"/>
       <c r="AN72" s="56"/>
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>25.452564102564107</v>
+        <v>25.404938271604941</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15156,7 +15274,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.47935535960456832</v>
+        <v>0.43172952864540193</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15255,17 +15373,19 @@
       <c r="AK73" s="56">
         <v>26.35</v>
       </c>
-      <c r="AL73" s="56"/>
+      <c r="AL73" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AM73" s="56"/>
       <c r="AN73" s="56"/>
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>25.786842105263158</v>
+        <v>25.862500000000001</v>
       </c>
       <c r="AR73" s="71" t="str">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15388,17 +15508,19 @@
       <c r="AK74" s="56">
         <v>20.55</v>
       </c>
-      <c r="AL74" s="56"/>
+      <c r="AL74" s="56">
+        <v>23.175000000000001</v>
+      </c>
       <c r="AM74" s="56"/>
       <c r="AN74" s="56"/>
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>20.837037037037039</v>
+        <v>20.920535714285712</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15406,7 +15528,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.83853828767692917</v>
+        <v>0.92203696492560283</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15521,17 +15643,19 @@
       <c r="AK75" s="56">
         <v>15.866666666666671</v>
       </c>
-      <c r="AL75" s="56"/>
+      <c r="AL75" s="56">
+        <v>16.466666666666669</v>
+      </c>
       <c r="AM75" s="56"/>
       <c r="AN75" s="56"/>
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>15.830864197530859</v>
+        <v>15.853571428571424</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15539,7 +15663,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.6498205055640689</v>
+        <v>0.67252773660463383</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15654,17 +15778,19 @@
       <c r="AK76" s="56">
         <v>20.149999999999999</v>
       </c>
-      <c r="AL76" s="56"/>
+      <c r="AL76" s="56">
+        <v>21.6</v>
+      </c>
       <c r="AM76" s="56"/>
       <c r="AN76" s="56"/>
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>20.69537037037037</v>
+        <v>20.727678571428573</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15672,7 +15798,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>0.89540375884415013</v>
+        <v>0.92771195990235356</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15787,17 +15913,19 @@
       <c r="AK77" s="56">
         <v>25.733333333333331</v>
       </c>
-      <c r="AL77" s="56"/>
+      <c r="AL77" s="56">
+        <v>25.4</v>
+      </c>
       <c r="AM77" s="56"/>
       <c r="AN77" s="56"/>
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>23.975308641975303</v>
+        <v>24.026190476190468</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15805,7 +15933,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.2920677859963838</v>
+        <v>1.3429496202115487</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15917,18 +16045,22 @@
       <c r="AJ78" s="56">
         <v>31.45</v>
       </c>
-      <c r="AK78" s="56"/>
-      <c r="AL78" s="56"/>
+      <c r="AK78" s="56">
+        <v>31.65</v>
+      </c>
+      <c r="AL78" s="56">
+        <v>31.85</v>
+      </c>
       <c r="AM78" s="56"/>
       <c r="AN78" s="56"/>
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>31.14423076923077</v>
+        <v>31.1875</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15936,7 +16068,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>1.960300958708121</v>
+        <v>2.003570189477351</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16047,17 +16179,19 @@
       <c r="AK79" s="56">
         <v>32.4</v>
       </c>
-      <c r="AL79" s="56"/>
+      <c r="AL79" s="56">
+        <v>32.6</v>
+      </c>
       <c r="AM79" s="56"/>
       <c r="AN79" s="56"/>
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.245333333333328</v>
+        <v>31.297435897435893</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16065,7 +16199,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>1.7762804488825985</v>
+        <v>1.8283830129851637</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16303,17 +16437,19 @@
       <c r="AK81" s="56">
         <v>25.15</v>
       </c>
-      <c r="AL81" s="56"/>
+      <c r="AL81" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AM81" s="56"/>
       <c r="AN81" s="56"/>
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v>24.168749999999992</v>
+        <v>24.209999999999994</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16321,7 +16457,7 @@
       </c>
       <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v>-5.8799060917777979E-3</v>
+        <v>3.5370093908223765E-2</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16433,18 +16569,22 @@
       <c r="AJ82" s="56">
         <v>27.466666666666669</v>
       </c>
-      <c r="AK82" s="56"/>
-      <c r="AL82" s="56"/>
+      <c r="AK82" s="56">
+        <v>26.86666666666666</v>
+      </c>
+      <c r="AL82" s="56">
+        <v>28.266666666666669</v>
+      </c>
       <c r="AM82" s="56"/>
       <c r="AN82" s="56"/>
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>26.175641025641028</v>
+        <v>26.275000000000002</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16452,7 +16592,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>1.0019185682194482</v>
+        <v>1.1012775425784227</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16707,17 +16847,19 @@
       <c r="AK85" s="56">
         <v>30.05</v>
       </c>
-      <c r="AL85" s="56"/>
+      <c r="AL85" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AM85" s="56"/>
       <c r="AN85" s="56"/>
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>30.802777777777774</v>
+        <v>30.786842105263155</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16840,17 +16982,19 @@
       <c r="AK86" s="56">
         <v>29.5</v>
       </c>
-      <c r="AL86" s="56"/>
+      <c r="AL86" s="56">
+        <v>30.1</v>
+      </c>
       <c r="AM86" s="56"/>
       <c r="AN86" s="56"/>
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.751851851851846</v>
+        <v>29.764285714285709</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16858,7 +17002,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.139768690297057</v>
+        <v>1.1522025527309196</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16973,17 +17117,19 @@
       <c r="AK87" s="56">
         <v>29.45</v>
       </c>
-      <c r="AL87" s="56"/>
+      <c r="AL87" s="56">
+        <v>30.7</v>
+      </c>
       <c r="AM87" s="56"/>
       <c r="AN87" s="56"/>
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>31.568518518518523</v>
+        <v>31.537500000000005</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16991,7 +17137,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>2.5623285460561327</v>
+        <v>2.5313100275376144</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17106,17 +17252,19 @@
       <c r="AK88" s="56">
         <v>30.25</v>
       </c>
-      <c r="AL88" s="56"/>
+      <c r="AL88" s="56">
+        <v>31.35</v>
+      </c>
       <c r="AM88" s="56"/>
       <c r="AN88" s="56"/>
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.13518518518519</v>
+        <v>30.178571428571434</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17124,7 +17272,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>1.4443105692097795</v>
+        <v>1.4876968125960239</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17227,17 +17375,19 @@
       <c r="AK89" s="56">
         <v>31.7</v>
       </c>
-      <c r="AL89" s="56"/>
+      <c r="AL89" s="56">
+        <v>32.900000000000013</v>
+      </c>
       <c r="AM89" s="56"/>
       <c r="AN89" s="56"/>
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>33.166666666666664</v>
+        <v>33.154545454545456</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17245,7 +17395,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>3.6841676250199633</v>
+        <v>3.6720464128987551</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17352,17 +17502,19 @@
       <c r="AK90" s="56">
         <v>29.35</v>
       </c>
-      <c r="AL90" s="56"/>
+      <c r="AL90" s="56">
+        <v>33</v>
+      </c>
       <c r="AM90" s="56"/>
       <c r="AN90" s="56"/>
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>31.954347826086959</v>
+        <v>31.997916666666669</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17370,7 +17522,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>2.9192877681742999</v>
+        <v>2.9628566087540094</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17467,17 +17619,19 @@
       <c r="AI91" s="56"/>
       <c r="AJ91" s="56"/>
       <c r="AK91" s="56"/>
-      <c r="AL91" s="56"/>
+      <c r="AL91" s="56">
+        <v>31.95</v>
+      </c>
       <c r="AM91" s="56"/>
       <c r="AN91" s="56"/>
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v>32.286111111111119</v>
+        <v>32.268421052631588</v>
       </c>
       <c r="AR91" s="71" t="str">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17600,17 +17754,19 @@
       <c r="AK92" s="56">
         <v>16.2</v>
       </c>
-      <c r="AL92" s="56"/>
+      <c r="AL92" s="56">
+        <v>16.55</v>
+      </c>
       <c r="AM92" s="56"/>
       <c r="AN92" s="56"/>
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.499382716049386</v>
+        <v>17.465476190476192</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17618,7 +17774,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.3360386300279146</v>
+        <v>1.3021321044547207</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17733,17 +17889,19 @@
       <c r="AK93" s="56">
         <v>23.666666666666671</v>
       </c>
-      <c r="AL93" s="56"/>
+      <c r="AL93" s="56">
+        <v>24.466666666666669</v>
+      </c>
       <c r="AM93" s="56"/>
       <c r="AN93" s="56"/>
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.619753086419749</v>
+        <v>23.65</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17751,7 +17909,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.5102652205501279</v>
+        <v>1.5405121341303776</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17866,17 +18024,19 @@
       <c r="AK94" s="56">
         <v>16.850000000000001</v>
       </c>
-      <c r="AL94" s="56"/>
+      <c r="AL94" s="56">
+        <v>17.2</v>
+      </c>
       <c r="AM94" s="56"/>
       <c r="AN94" s="56"/>
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.26018518518519</v>
+        <v>17.258035714285718</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17884,7 +18044,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.1649580392506209</v>
+        <v>1.1628085683511493</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17999,17 +18159,19 @@
       <c r="AK95" s="56">
         <v>15.05</v>
       </c>
-      <c r="AL95" s="56"/>
+      <c r="AL95" s="56">
+        <v>14.1</v>
+      </c>
       <c r="AM95" s="56"/>
       <c r="AN95" s="56"/>
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.687037037037037</v>
+        <v>14.66607142857143</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18017,7 +18179,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.0542289008851764</v>
+        <v>1.0332632924195693</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18290,17 +18452,19 @@
       <c r="AK98" s="56">
         <v>12.45</v>
       </c>
-      <c r="AL98" s="56"/>
+      <c r="AL98" s="56">
+        <v>12.2</v>
+      </c>
       <c r="AM98" s="56"/>
       <c r="AN98" s="56"/>
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.138888888888889</v>
+        <v>13.105357142857143</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18419,17 +18583,19 @@
       <c r="AK99" s="56">
         <v>14.9</v>
       </c>
-      <c r="AL99" s="56"/>
+      <c r="AL99" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AM99" s="56"/>
       <c r="AN99" s="56"/>
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.477333333333336</v>
+        <v>14.482051282051286</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18538,17 +18704,19 @@
       <c r="AK100" s="56">
         <v>15.266666666666669</v>
       </c>
-      <c r="AL100" s="56"/>
+      <c r="AL100" s="56">
+        <v>15.733333333333331</v>
+      </c>
       <c r="AM100" s="56"/>
       <c r="AN100" s="56"/>
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v>16.196666666666665</v>
+        <v>16.174603174603174</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18556,7 +18724,7 @@
       </c>
       <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v>1.8873087605586747</v>
+        <v>1.8652452684951832</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18786,17 +18954,19 @@
       <c r="AK102" s="56">
         <v>12.733333333333331</v>
       </c>
-      <c r="AL102" s="56"/>
+      <c r="AL102" s="56">
+        <v>13.2</v>
+      </c>
       <c r="AM102" s="56"/>
       <c r="AN102" s="56"/>
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>13.025000000000004</v>
+        <v>13.032000000000004</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18804,7 +18974,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>1.7780046306141131</v>
+        <v>1.7850046306141127</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19071,17 +19241,19 @@
       <c r="AK105" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="AL105" s="56"/>
+      <c r="AL105" s="56">
+        <v>17.533333333333331</v>
+      </c>
       <c r="AM105" s="56"/>
       <c r="AN105" s="56"/>
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.194444444444446</v>
+        <v>18.168000000000003</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19089,7 +19261,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.1499069359681755</v>
+        <v>1.1234624915237319</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19259,17 +19431,19 @@
       <c r="AK107" s="56">
         <v>12.2</v>
       </c>
-      <c r="AL107" s="56"/>
+      <c r="AL107" s="56">
+        <v>13.133333333333329</v>
+      </c>
       <c r="AM107" s="56"/>
       <c r="AN107" s="56"/>
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ107" s="71">
         <f t="shared" si="4"/>
-        <v>14.951111111111114</v>
+        <v>14.837500000000002</v>
       </c>
       <c r="AR107" s="71">
         <f>IFERROR(VLOOKUP(A107,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19277,7 +19451,7 @@
       </c>
       <c r="AS107" s="71">
         <f t="shared" si="5"/>
-        <v>1.5307945041816442</v>
+        <v>1.4171833930705322</v>
       </c>
     </row>
     <row r="108" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19392,17 +19566,19 @@
       <c r="AK108" s="56">
         <v>13.25</v>
       </c>
-      <c r="AL108" s="56"/>
+      <c r="AL108" s="56">
+        <v>13.85</v>
+      </c>
       <c r="AM108" s="56"/>
       <c r="AN108" s="56"/>
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>14.21851851851852</v>
+        <v>14.205357142857144</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19410,7 +19586,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>-1.0514396213290311E-2</v>
+        <v>-2.3675771874666296E-2</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19525,17 +19701,19 @@
       <c r="AK109" s="56">
         <v>14.2</v>
       </c>
-      <c r="AL109" s="56"/>
+      <c r="AL109" s="56">
+        <v>14.95</v>
+      </c>
       <c r="AM109" s="56"/>
       <c r="AN109" s="56"/>
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.557407407407405</v>
+        <v>14.571428571428569</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19543,7 +19721,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.84364431989961552</v>
+        <v>0.85766548392077979</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19658,17 +19836,19 @@
       <c r="AK110" s="56">
         <v>18.333333333333329</v>
       </c>
-      <c r="AL110" s="56"/>
+      <c r="AL110" s="56">
+        <v>17.93333333333333</v>
+      </c>
       <c r="AM110" s="56"/>
       <c r="AN110" s="56"/>
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.528395061728389</v>
+        <v>17.542857142857137</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19676,7 +19856,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.59343302326150038</v>
+        <v>0.60789510439024852</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19791,17 +19971,19 @@
       <c r="AK111" s="56">
         <v>15</v>
       </c>
-      <c r="AL111" s="56"/>
+      <c r="AL111" s="56">
+        <v>15.133333333333329</v>
+      </c>
       <c r="AM111" s="56"/>
       <c r="AN111" s="56"/>
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.922222222222226</v>
+        <v>15.894047619047623</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19809,7 +19991,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.41985869864903691</v>
+        <v>0.39168409547443339</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19924,17 +20106,19 @@
       <c r="AK112" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="AL112" s="56"/>
+      <c r="AL112" s="56">
+        <v>18.266666666666669</v>
+      </c>
       <c r="AM112" s="56"/>
       <c r="AN112" s="56"/>
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>17.832098765432097</v>
+        <v>17.847619047619045</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19942,7 +20126,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.4524025043300171</v>
+        <v>1.4679227865169651</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20055,17 +20239,19 @@
       <c r="AK113" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="AL113" s="56"/>
+      <c r="AL113" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AM113" s="56"/>
       <c r="AN113" s="56"/>
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>19.015384615384615</v>
+        <v>19.022222222222222</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20073,7 +20259,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>0.89099714782808448</v>
+        <v>0.89783475466569129</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20154,13 +20340,15 @@
       <c r="AK114" s="56">
         <v>21.466666666666669</v>
       </c>
-      <c r="AL114" s="56"/>
+      <c r="AL114" s="56">
+        <v>22.666666666666671</v>
+      </c>
       <c r="AM114" s="56"/>
       <c r="AN114" s="56"/>
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -20287,17 +20475,19 @@
       <c r="AK115" s="56">
         <v>27.85</v>
       </c>
-      <c r="AL115" s="56"/>
+      <c r="AL115" s="56">
+        <v>28.25</v>
+      </c>
       <c r="AM115" s="56"/>
       <c r="AN115" s="56"/>
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.265740740740739</v>
+        <v>26.33660714285714</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20305,7 +20495,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.42126076298771764</v>
+        <v>0.4921271651041188</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20416,17 +20606,19 @@
       <c r="AK116" s="56">
         <v>19.8</v>
       </c>
-      <c r="AL116" s="56"/>
+      <c r="AL116" s="56">
+        <v>19.266666666666669</v>
+      </c>
       <c r="AM116" s="56"/>
       <c r="AN116" s="56"/>
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.250666666666667</v>
+        <v>19.251282051282054</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20434,7 +20626,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.85416150032584781</v>
+        <v>0.85477688494123427</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20549,17 +20741,19 @@
       <c r="AK117" s="56">
         <v>27.533333333333331</v>
       </c>
-      <c r="AL117" s="56"/>
+      <c r="AL117" s="56">
+        <v>28.2</v>
+      </c>
       <c r="AM117" s="56"/>
       <c r="AN117" s="56"/>
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>26.224691358024693</v>
+        <v>26.295238095238098</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20567,7 +20761,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.85585175228994359</v>
+        <v>0.9263984895033488</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20682,17 +20876,19 @@
       <c r="AK118" s="56">
         <v>29.93333333333333</v>
       </c>
-      <c r="AL118" s="56"/>
+      <c r="AL118" s="56">
+        <v>30.4</v>
+      </c>
       <c r="AM118" s="56"/>
       <c r="AN118" s="56"/>
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ118" s="71">
         <f t="shared" si="4"/>
-        <v>28.725925925925928</v>
+        <v>28.785714285714285</v>
       </c>
       <c r="AR118" s="71">
         <f>IFERROR(VLOOKUP(A118,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20700,7 +20896,7 @@
       </c>
       <c r="AS118" s="71">
         <f t="shared" si="5"/>
-        <v>2.9726463560334686</v>
+        <v>3.0324347158218252</v>
       </c>
     </row>
     <row r="119" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20815,17 +21011,19 @@
       <c r="AK119" s="56">
         <v>23.8</v>
       </c>
-      <c r="AL119" s="56"/>
+      <c r="AL119" s="56">
+        <v>23.2</v>
+      </c>
       <c r="AM119" s="56"/>
       <c r="AN119" s="56"/>
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ119" s="71">
         <f t="shared" si="4"/>
-        <v>23.624691358024691</v>
+        <v>23.609523809523811</v>
       </c>
       <c r="AR119" s="71">
         <f>IFERROR(VLOOKUP(A119,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20833,7 +21031,7 @@
       </c>
       <c r="AS119" s="71">
         <f t="shared" si="5"/>
-        <v>1.8962504978096817</v>
+        <v>1.8810829493088015</v>
       </c>
     </row>
     <row r="120" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21128,17 +21326,19 @@
       <c r="AK122" s="56">
         <v>10.066666666666659</v>
       </c>
-      <c r="AL122" s="56"/>
+      <c r="AL122" s="56">
+        <v>11.8</v>
+      </c>
       <c r="AM122" s="56"/>
       <c r="AN122" s="56"/>
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.060493827160494</v>
+        <v>12.051190476190476</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21146,7 +21346,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.7577368311902148</v>
+        <v>1.7484334802201964</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21903,18 +22103,22 @@
       <c r="AJ130" s="56">
         <v>14.4</v>
       </c>
-      <c r="AK130" s="56"/>
-      <c r="AL130" s="56"/>
+      <c r="AK130" s="56">
+        <v>16.06666666666667</v>
+      </c>
+      <c r="AL130" s="56">
+        <v>15.96666666666667</v>
+      </c>
       <c r="AM130" s="56"/>
       <c r="AN130" s="56"/>
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ130" s="71">
         <f t="shared" si="4"/>
-        <v>15.805128205128206</v>
+        <v>15.820238095238096</v>
       </c>
       <c r="AR130" s="71">
         <f>IFERROR(VLOOKUP(A130,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21922,7 +22126,7 @@
       </c>
       <c r="AS130" s="71">
         <f t="shared" si="5"/>
-        <v>1.5518858306607566</v>
+        <v>1.5669957207706471</v>
       </c>
     </row>
     <row r="131" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22037,17 +22241,19 @@
       <c r="AK131" s="56">
         <v>17.55</v>
       </c>
-      <c r="AL131" s="56"/>
+      <c r="AL131" s="56">
+        <v>18</v>
+      </c>
       <c r="AM131" s="56"/>
       <c r="AN131" s="56"/>
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.30740740740741</v>
+        <v>18.296428571428574</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22055,7 +22261,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.5145104085034617</v>
+        <v>1.5035315725246257</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22247,19 +22453,21 @@
         <v>13.2</v>
       </c>
       <c r="AK133" s="56">
-        <v>14.33333333333333</v>
-      </c>
-      <c r="AL133" s="56"/>
+        <v>14.266666666666669</v>
+      </c>
+      <c r="AL133" s="56">
+        <v>13.43333333333333</v>
+      </c>
       <c r="AM133" s="56"/>
       <c r="AN133" s="56"/>
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>13.887654320987652</v>
+        <v>13.869047619047617</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22267,7 +22475,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.2523145463338121</v>
+        <v>1.233707844393777</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22382,17 +22590,19 @@
       <c r="AK134" s="56">
         <v>16.8</v>
       </c>
-      <c r="AL134" s="56"/>
+      <c r="AL134" s="56">
+        <v>17.466666666666669</v>
+      </c>
       <c r="AM134" s="56"/>
       <c r="AN134" s="56"/>
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>17.795061728395062</v>
+        <v>17.783333333333331</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22400,7 +22610,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.2128828860113927</v>
+        <v>2.2011544909496621</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22515,17 +22725,19 @@
       <c r="AK135" s="56">
         <v>18.850000000000001</v>
       </c>
-      <c r="AL135" s="56"/>
+      <c r="AL135" s="56">
+        <v>21.25</v>
+      </c>
       <c r="AM135" s="56"/>
       <c r="AN135" s="56"/>
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>20.6</v>
+        <v>20.623214285714287</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22533,7 +22745,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>1.9181193625948723</v>
+        <v>1.9413336483091577</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22858,17 +23070,19 @@
       <c r="AK138" s="56">
         <v>21.666666666666671</v>
       </c>
-      <c r="AL138" s="56"/>
+      <c r="AL138" s="56">
+        <v>22.533333333333331</v>
+      </c>
       <c r="AM138" s="56"/>
       <c r="AN138" s="56"/>
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>22.158024691358023</v>
+        <v>22.171428571428571</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22876,7 +23090,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.1478035940096234</v>
+        <v>2.1612074740801717</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22991,17 +23205,19 @@
       <c r="AK139" s="56">
         <v>14.3</v>
       </c>
-      <c r="AL139" s="56"/>
+      <c r="AL139" s="56">
+        <v>13.35</v>
+      </c>
       <c r="AM139" s="56"/>
       <c r="AN139" s="56"/>
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>14.015740740740739</v>
+        <v>13.991964285714285</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23009,7 +23225,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.1115229679067298</v>
+        <v>1.0877465128802761</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23124,17 +23340,19 @@
       <c r="AK140" s="56">
         <v>15.95</v>
       </c>
-      <c r="AL140" s="56"/>
+      <c r="AL140" s="56">
+        <v>15.15</v>
+      </c>
       <c r="AM140" s="56"/>
       <c r="AN140" s="56"/>
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.385185185185186</v>
+        <v>16.341071428571428</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23142,7 +23360,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.79083461341526551</v>
+        <v>0.74672085680150779</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23257,17 +23475,19 @@
       <c r="AK141" s="56">
         <v>13.6</v>
       </c>
-      <c r="AL141" s="56"/>
+      <c r="AL141" s="56">
+        <v>13.53333333333333</v>
+      </c>
       <c r="AM141" s="56"/>
       <c r="AN141" s="56"/>
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.427160493827163</v>
+        <v>13.430952380952382</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23275,7 +23495,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.4131310969891135</v>
+        <v>1.4169229841143327</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23388,17 +23608,19 @@
       <c r="AK142" s="56">
         <v>11.675000000000001</v>
       </c>
-      <c r="AL142" s="56"/>
+      <c r="AL142" s="56">
+        <v>11</v>
+      </c>
       <c r="AM142" s="56"/>
       <c r="AN142" s="56"/>
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>11.601923076923079</v>
+        <v>11.579629629629631</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23406,7 +23628,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.072937100441278</v>
+        <v>1.05064365314783</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23521,17 +23743,19 @@
       <c r="AK143" s="56">
         <v>27.733333333333331</v>
       </c>
-      <c r="AL143" s="56"/>
+      <c r="AL143" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="AM143" s="56"/>
       <c r="AN143" s="56"/>
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.676543209876542</v>
+        <v>27.704761904761906</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23539,7 +23763,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>1.8146031177106607</v>
+        <v>1.842821812596025</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23650,17 +23874,19 @@
       <c r="AK144" s="56">
         <v>14.6</v>
       </c>
-      <c r="AL144" s="56"/>
+      <c r="AL144" s="56">
+        <v>15.46666666666667</v>
+      </c>
       <c r="AM144" s="56"/>
       <c r="AN144" s="56"/>
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>15.594666666666667</v>
+        <v>15.589743589743591</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23668,7 +23894,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>-0.11821908724762231</v>
+        <v>-0.12314216417069801</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23783,17 +24009,19 @@
       <c r="AK145" s="56">
         <v>20.2</v>
       </c>
-      <c r="AL145" s="56"/>
+      <c r="AL145" s="56">
+        <v>20.466666666666669</v>
+      </c>
       <c r="AM145" s="56"/>
       <c r="AN145" s="56"/>
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>19.471604938271607</v>
+        <v>19.50714285714286</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23801,7 +24029,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>0.4295884037734865</v>
+        <v>0.46512632264473908</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24046,18 +24274,22 @@
       <c r="AJ147" s="56">
         <v>25.333333333333329</v>
       </c>
-      <c r="AK147" s="56"/>
-      <c r="AL147" s="56"/>
+      <c r="AK147" s="56">
+        <v>25.266666666666669</v>
+      </c>
+      <c r="AL147" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="AM147" s="56"/>
       <c r="AN147" s="56"/>
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.182051282051287</v>
+        <v>25.238095238095241</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24065,7 +24297,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.6779937901879265</v>
+        <v>1.7340377462318806</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24176,17 +24408,19 @@
       <c r="AK148" s="56">
         <v>29.8</v>
       </c>
-      <c r="AL148" s="56"/>
+      <c r="AL148" s="56">
+        <v>31.6</v>
+      </c>
       <c r="AM148" s="56"/>
       <c r="AN148" s="56"/>
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.30533333333333</v>
+        <v>30.355128205128203</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24194,7 +24428,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.6638021024785488</v>
+        <v>1.7135969742734218</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24309,17 +24543,19 @@
       <c r="AK149" s="56">
         <v>22.93333333333333</v>
       </c>
-      <c r="AL149" s="56"/>
+      <c r="AL149" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="AM149" s="56"/>
       <c r="AN149" s="56"/>
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.501234567901232</v>
+        <v>23.507142857142856</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24327,7 +24563,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.625166794948381</v>
+        <v>1.6310750841900052</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24517,17 +24753,19 @@
       <c r="AK151" s="56">
         <v>23</v>
       </c>
-      <c r="AL151" s="56"/>
+      <c r="AL151" s="56">
+        <v>23.8</v>
+      </c>
       <c r="AM151" s="56"/>
       <c r="AN151" s="56"/>
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ151" s="71">
         <f t="shared" si="7"/>
-        <v>23.234666666666662</v>
+        <v>23.256410256410252</v>
       </c>
       <c r="AR151" s="71">
         <f>IFERROR(VLOOKUP(A151,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24535,7 +24773,7 @@
       </c>
       <c r="AS151" s="71">
         <f t="shared" si="8"/>
-        <v>1.4220793880460221</v>
+        <v>1.4438229777896119</v>
       </c>
     </row>
     <row r="152" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24808,17 +25046,19 @@
       <c r="AK154" s="56">
         <v>20.100000000000001</v>
       </c>
-      <c r="AL154" s="56"/>
+      <c r="AL154" s="56">
+        <v>20.45</v>
+      </c>
       <c r="AM154" s="56"/>
       <c r="AN154" s="56"/>
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>20.453703703703702</v>
+        <v>20.453571428571429</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24826,7 +25066,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>0.94008294930876346</v>
+        <v>0.93995067417649025</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24941,17 +25181,19 @@
       <c r="AK155" s="56">
         <v>27.6</v>
       </c>
-      <c r="AL155" s="56"/>
+      <c r="AL155" s="56">
+        <v>29.666666666666671</v>
+      </c>
       <c r="AM155" s="56"/>
       <c r="AN155" s="56"/>
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>28.829629629629629</v>
+        <v>28.859523809523807</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24959,7 +25201,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.1068430687738307</v>
+        <v>1.136737248668009</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25272,17 +25514,19 @@
       <c r="AK158" s="56">
         <v>29.733333333333331</v>
       </c>
-      <c r="AL158" s="56"/>
+      <c r="AL158" s="56">
+        <v>31</v>
+      </c>
       <c r="AM158" s="56"/>
       <c r="AN158" s="56"/>
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>29.997222222222231</v>
+        <v>30.03733333333334</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25290,7 +25534,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>1.9788100551420307</v>
+        <v>2.0189211662531399</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25399,17 +25643,19 @@
       <c r="AK159" s="56">
         <v>19.666666666666671</v>
       </c>
-      <c r="AL159" s="56"/>
+      <c r="AL159" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AM159" s="56"/>
       <c r="AN159" s="56"/>
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.284722222222225</v>
+        <v>20.281333333333336</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25417,7 +25663,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.293785107531825</v>
+        <v>1.2903962186429361</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25530,17 +25776,19 @@
       <c r="AK160" s="56">
         <v>26.86666666666666</v>
       </c>
-      <c r="AL160" s="56"/>
+      <c r="AL160" s="56">
+        <v>27.8</v>
+      </c>
       <c r="AM160" s="56"/>
       <c r="AN160" s="56"/>
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.028205128205137</v>
+        <v>27.056790123456796</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25639,17 +25887,19 @@
         <v>18.533333333333331</v>
       </c>
       <c r="AK161" s="56"/>
-      <c r="AL161" s="56"/>
+      <c r="AL161" s="56">
+        <v>19.866666666666671</v>
+      </c>
       <c r="AM161" s="56"/>
       <c r="AN161" s="56"/>
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ161" s="71">
         <f t="shared" si="7"/>
-        <v>19.137777777777782</v>
+        <v>19.183333333333337</v>
       </c>
       <c r="AR161" s="71">
         <f>IFERROR(VLOOKUP(A161,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25657,7 +25907,7 @@
       </c>
       <c r="AS161" s="71">
         <f t="shared" si="8"/>
-        <v>1.5778977121287312</v>
+        <v>1.6234532676842868</v>
       </c>
     </row>
     <row r="162" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25772,17 +26022,19 @@
       <c r="AK162" s="56">
         <v>28.13333333333334</v>
       </c>
-      <c r="AL162" s="56"/>
+      <c r="AL162" s="56">
+        <v>29.06666666666667</v>
+      </c>
       <c r="AM162" s="56"/>
       <c r="AN162" s="56"/>
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>28.871604938271613</v>
+        <v>28.878571428571437</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25790,7 +26042,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.29806755039733446</v>
+        <v>0.30503404069715856</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25905,17 +26157,19 @@
       <c r="AK163" s="56">
         <v>21.666666666666671</v>
       </c>
-      <c r="AL163" s="56"/>
+      <c r="AL163" s="56">
+        <v>21.533333333333331</v>
+      </c>
       <c r="AM163" s="56"/>
       <c r="AN163" s="56"/>
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.412345679012347</v>
+        <v>21.416666666666664</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25923,7 +26177,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.16292186341176773</v>
+        <v>0.16724285106608505</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26038,17 +26292,19 @@
       <c r="AK164" s="56">
         <v>24.85</v>
       </c>
-      <c r="AL164" s="56"/>
+      <c r="AL164" s="56">
+        <v>25.15</v>
+      </c>
       <c r="AM164" s="56"/>
       <c r="AN164" s="56"/>
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.390740740740743</v>
+        <v>25.38214285714286</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26056,7 +26312,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.5928131315806624</v>
+        <v>1.5842152479827796</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26246,17 +26502,19 @@
       <c r="AK166" s="56">
         <v>13.2</v>
       </c>
-      <c r="AL166" s="56"/>
+      <c r="AL166" s="56">
+        <v>15.133333333333329</v>
+      </c>
       <c r="AM166" s="56"/>
       <c r="AN166" s="56"/>
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.71466666666667</v>
+        <v>14.730769230769234</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26264,7 +26522,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.116197132616529</v>
+        <v>1.1322996967190928</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26375,17 +26633,19 @@
       <c r="AK167" s="56">
         <v>20.2</v>
       </c>
-      <c r="AL167" s="56"/>
+      <c r="AL167" s="56">
+        <v>20.93333333333333</v>
+      </c>
       <c r="AM167" s="56"/>
       <c r="AN167" s="56"/>
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.65066666666667</v>
+        <v>20.661538461538463</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26393,7 +26653,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.6150988570560294</v>
+        <v>1.6259706519278225</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26504,17 +26764,19 @@
       <c r="AK168" s="56">
         <v>27.2</v>
       </c>
-      <c r="AL168" s="56"/>
+      <c r="AL168" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AM168" s="56"/>
       <c r="AN168" s="56"/>
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.776000000000007</v>
+        <v>27.826923076923087</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26522,7 +26784,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.7101355339334283</v>
+        <v>1.7610586108565087</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26637,17 +26899,19 @@
       <c r="AK169" s="56">
         <v>9.1999999999999993</v>
       </c>
-      <c r="AL169" s="56"/>
+      <c r="AL169" s="56">
+        <v>9.9</v>
+      </c>
       <c r="AM169" s="56"/>
       <c r="AN169" s="56"/>
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>8.9870370370370356</v>
+        <v>9.0196428571428573</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26655,7 +26919,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.44491275568249833</v>
+        <v>0.47751857578832002</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26754,17 +27018,19 @@
       <c r="AK170" s="56">
         <v>25.733333333333331</v>
       </c>
-      <c r="AL170" s="56"/>
+      <c r="AL170" s="56">
+        <v>27.266666666666669</v>
+      </c>
       <c r="AM170" s="56"/>
       <c r="AN170" s="56"/>
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v>24.807017543859647</v>
+        <v>24.93</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26772,7 +27038,7 @@
       </c>
       <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v>0.71639360199717572</v>
+        <v>0.83937605813752825</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26885,17 +27151,19 @@
       <c r="AK171" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="AL171" s="56"/>
+      <c r="AL171" s="56">
+        <v>21.6</v>
+      </c>
       <c r="AM171" s="56"/>
       <c r="AN171" s="56"/>
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>20.707692307692305</v>
+        <v>20.74074074074074</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26903,7 +27171,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.778766285440387</v>
+        <v>1.8118147184888223</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27014,17 +27282,19 @@
       <c r="AK172" s="56">
         <v>25.95</v>
       </c>
-      <c r="AL172" s="56"/>
+      <c r="AL172" s="56">
+        <v>27.35</v>
+      </c>
       <c r="AM172" s="56"/>
       <c r="AN172" s="56"/>
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.67</v>
+        <v>25.734615384615385</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27032,7 +27302,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.2313716314881233</v>
+        <v>1.2959870161035063</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27147,17 +27417,19 @@
       <c r="AK173" s="56">
         <v>24.5</v>
       </c>
-      <c r="AL173" s="56"/>
+      <c r="AL173" s="56">
+        <v>25.45</v>
+      </c>
       <c r="AM173" s="56"/>
       <c r="AN173" s="56"/>
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.100308641975314</v>
+        <v>25.112797619047626</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27165,7 +27437,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.0459000398247831</v>
+        <v>1.0583890168970953</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27278,17 +27550,19 @@
       <c r="AK174" s="56">
         <v>15</v>
       </c>
-      <c r="AL174" s="56"/>
+      <c r="AL174" s="56">
+        <v>14.2</v>
+      </c>
       <c r="AM174" s="56"/>
       <c r="AN174" s="56"/>
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ174" s="71">
         <f t="shared" si="7"/>
-        <v>13.923076923076925</v>
+        <v>13.933333333333335</v>
       </c>
       <c r="AR174" s="71">
         <f>IFERROR(VLOOKUP(A174,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27296,7 +27570,7 @@
       </c>
       <c r="AS174" s="71">
         <f t="shared" si="8"/>
-        <v>1.8623250654050647</v>
+        <v>1.8725814756614749</v>
       </c>
     </row>
     <row r="175" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27680,17 +27954,19 @@
       <c r="AK178" s="56">
         <v>25.4</v>
       </c>
-      <c r="AL178" s="56"/>
+      <c r="AL178" s="56">
+        <v>26.733333333333331</v>
+      </c>
       <c r="AM178" s="56"/>
       <c r="AN178" s="56"/>
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>25.133333333333329</v>
+        <v>25.202898550724637</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27698,7 +27974,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.58105298645443781</v>
+        <v>0.65061820384574531</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27805,17 +28081,19 @@
       <c r="AK179" s="56">
         <v>17.5</v>
       </c>
-      <c r="AL179" s="56"/>
+      <c r="AL179" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AM179" s="56"/>
       <c r="AN179" s="56"/>
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>18.526086956521738</v>
+        <v>18.554166666666664</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27823,7 +28101,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>0.93850327300508596</v>
+        <v>0.9665829831500119</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28017,17 +28295,19 @@
       <c r="AK181" s="56">
         <v>31.6</v>
       </c>
-      <c r="AL181" s="56"/>
+      <c r="AL181" s="56">
+        <v>32.266666666666673</v>
+      </c>
       <c r="AM181" s="56"/>
       <c r="AN181" s="56"/>
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ181" s="71">
         <f t="shared" si="7"/>
-        <v>30.965432098765429</v>
+        <v>31.011904761904759</v>
       </c>
       <c r="AR181" s="71">
         <f>IFERROR(VLOOKUP(A181,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28035,7 +28315,7 @@
       </c>
       <c r="AS181" s="71">
         <f t="shared" si="8"/>
-        <v>2.4321957111956181</v>
+        <v>2.4786683743349478</v>
       </c>
     </row>
     <row r="182" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28308,17 +28588,19 @@
       <c r="AK184" s="56">
         <v>27.8</v>
       </c>
-      <c r="AL184" s="56"/>
+      <c r="AL184" s="56">
+        <v>29.36666666666666</v>
+      </c>
       <c r="AM184" s="56"/>
       <c r="AN184" s="56"/>
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>28.098765432098769</v>
+        <v>28.144047619047623</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28326,7 +28608,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.4603942144817808</v>
+        <v>1.5056764014306339</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28433,17 +28715,19 @@
       <c r="AK185" s="56">
         <v>29</v>
       </c>
-      <c r="AL185" s="56"/>
+      <c r="AL185" s="56">
+        <v>29.06666666666667</v>
+      </c>
       <c r="AM185" s="56"/>
       <c r="AN185" s="56"/>
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ185" s="71">
         <f t="shared" si="7"/>
-        <v>28.93333333333333</v>
+        <v>28.938888888888886</v>
       </c>
       <c r="AR185" s="71">
         <f>IFERROR(VLOOKUP(A185,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28451,7 +28735,7 @@
       </c>
       <c r="AS185" s="71">
         <f t="shared" si="8"/>
-        <v>1.324701048321959</v>
+        <v>1.3302566038775154</v>
       </c>
     </row>
     <row r="186" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28724,17 +29008,19 @@
       <c r="AK188" s="56">
         <v>16.93333333333333</v>
       </c>
-      <c r="AL188" s="56"/>
+      <c r="AL188" s="56">
+        <v>16.93333333333333</v>
+      </c>
       <c r="AM188" s="56"/>
       <c r="AN188" s="56"/>
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>17.30123456790124</v>
+        <v>17.288095238095242</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28742,7 +29028,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.3056425783695094</v>
+        <v>1.2925032485635111</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28978,17 +29264,19 @@
       <c r="AK190" s="56">
         <v>30.666666666666671</v>
       </c>
-      <c r="AL190" s="56"/>
+      <c r="AL190" s="56">
+        <v>30.333333333333329</v>
+      </c>
       <c r="AM190" s="56"/>
       <c r="AN190" s="56"/>
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>30.53827160493827</v>
+        <v>30.530952380952382</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28996,7 +29284,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.6217479434558015</v>
+        <v>1.6144287194699132</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29111,17 +29399,19 @@
       <c r="AK191" s="56">
         <v>17.2</v>
       </c>
-      <c r="AL191" s="56"/>
+      <c r="AL191" s="56">
+        <v>18.75</v>
+      </c>
       <c r="AM191" s="56"/>
       <c r="AN191" s="56"/>
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.548148148148144</v>
+        <v>18.55535714285714</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29129,7 +29419,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.1609291334875351</v>
+        <v>1.1681381281965315</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29244,17 +29534,19 @@
       <c r="AK192" s="56">
         <v>27.333333333333329</v>
       </c>
-      <c r="AL192" s="56"/>
+      <c r="AL192" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AM192" s="56"/>
       <c r="AN192" s="56"/>
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.195061728395075</v>
+        <v>26.230952380952395</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29262,7 +29554,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.95055454757690327</v>
+        <v>0.98644520013422365</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29368,18 +29660,22 @@
       <c r="AJ193" s="56">
         <v>26.55</v>
       </c>
-      <c r="AK193" s="56"/>
-      <c r="AL193" s="56"/>
+      <c r="AK193" s="56">
+        <v>28.45</v>
+      </c>
+      <c r="AL193" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AM193" s="56"/>
       <c r="AN193" s="56"/>
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>27.063043478260866</v>
+        <v>27.187999999999999</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29387,7 +29683,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>0.71027393825169582</v>
+        <v>0.83523045999082868</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29502,17 +29798,19 @@
       <c r="AK194" s="56">
         <v>20.399999999999999</v>
       </c>
-      <c r="AL194" s="56"/>
+      <c r="AL194" s="56">
+        <v>22.8</v>
+      </c>
       <c r="AM194" s="56"/>
       <c r="AN194" s="56"/>
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.165432098765432</v>
+        <v>21.223809523809525</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29520,7 +29818,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-0.44222969829299785</v>
+        <v>-0.38385227324890536</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29635,17 +29933,19 @@
       <c r="AK195" s="56">
         <v>25.86666666666666</v>
       </c>
-      <c r="AL195" s="56"/>
+      <c r="AL195" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="AM195" s="56"/>
       <c r="AN195" s="56"/>
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>27.572839506172841</v>
+        <v>27.547619047619047</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29653,7 +29953,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>1.8853512964630816</v>
+        <v>1.8601308379092885</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29768,17 +30068,19 @@
       <c r="AK196" s="56">
         <v>20.6</v>
       </c>
-      <c r="AL196" s="56"/>
+      <c r="AL196" s="56">
+        <v>21.533333333333331</v>
+      </c>
       <c r="AM196" s="56"/>
       <c r="AN196" s="56"/>
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>22.069135802469141</v>
+        <v>22.050000000000004</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29786,7 +30088,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>1.8453793309438709</v>
+        <v>1.826243528474734</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29901,17 +30203,19 @@
       <c r="AK197" s="56">
         <v>26.6</v>
       </c>
-      <c r="AL197" s="56"/>
+      <c r="AL197" s="56">
+        <v>26.6</v>
+      </c>
       <c r="AM197" s="56"/>
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.911111111111111</v>
+        <v>25.935714285714287</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29919,7 +30223,7 @@
       </c>
       <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.7837281099405828</v>
+        <v>1.8083312845437582</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30034,17 +30338,19 @@
       <c r="AK198" s="56">
         <v>20.95</v>
       </c>
-      <c r="AL198" s="56"/>
+      <c r="AL198" s="56">
+        <v>21.8</v>
+      </c>
       <c r="AM198" s="56"/>
       <c r="AN198" s="56"/>
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.596296296296291</v>
+        <v>21.603571428571424</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30167,17 +30473,19 @@
       <c r="AK199" s="56">
         <v>16.13333333333334</v>
       </c>
-      <c r="AL199" s="56"/>
+      <c r="AL199" s="56">
+        <v>16.399999999999999</v>
+      </c>
       <c r="AM199" s="56"/>
       <c r="AN199" s="56"/>
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.575308641975308</v>
+        <v>16.569047619047616</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30185,7 +30493,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.78764823578411836</v>
+        <v>0.78138721285642632</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30300,17 +30608,19 @@
       <c r="AK200" s="56">
         <v>14</v>
       </c>
-      <c r="AL200" s="56"/>
+      <c r="AL200" s="56">
+        <v>14.15</v>
+      </c>
       <c r="AM200" s="56"/>
       <c r="AN200" s="56"/>
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.642592592592594</v>
+        <v>14.625</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30318,7 +30628,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.2769801248089543</v>
+        <v>1.2593875322163601</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30433,17 +30743,19 @@
       <c r="AK201" s="56">
         <v>26.35</v>
       </c>
-      <c r="AL201" s="56"/>
+      <c r="AL201" s="56">
+        <v>26.85</v>
+      </c>
       <c r="AM201" s="56"/>
       <c r="AN201" s="56"/>
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>27.083333333333329</v>
+        <v>27.074999999999996</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30451,7 +30763,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>1.5458040650024785</v>
+        <v>1.5374707316691456</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30547,18 +30859,20 @@
       </c>
       <c r="AI202" s="56"/>
       <c r="AJ202" s="56"/>
-      <c r="AK202" s="56"/>
+      <c r="AK202" s="56">
+        <v>12.5</v>
+      </c>
       <c r="AL202" s="56"/>
       <c r="AM202" s="56"/>
       <c r="AN202" s="56"/>
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ202" s="71">
         <f t="shared" si="10"/>
-        <v>13.502777777777776</v>
+        <v>13.45</v>
       </c>
       <c r="AR202" s="71">
         <f>IFERROR(VLOOKUP(A202,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30566,7 +30880,7 @@
       </c>
       <c r="AS202" s="71">
         <f t="shared" si="11"/>
-        <v>0.69921381927385617</v>
+        <v>0.64643604149607903</v>
       </c>
     </row>
     <row r="203" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30907,17 +31221,19 @@
       <c r="AK205" s="56">
         <v>14.35</v>
       </c>
-      <c r="AL205" s="56"/>
+      <c r="AL205" s="56">
+        <v>14.55</v>
+      </c>
       <c r="AM205" s="56"/>
       <c r="AN205" s="56"/>
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>14.537037037037036</v>
+        <v>14.5375</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30925,7 +31241,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.1221429202193658</v>
+        <v>1.1226058831823291</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31143,17 +31459,19 @@
       <c r="AK207" s="56">
         <v>14.53333333333333</v>
       </c>
-      <c r="AL207" s="56"/>
+      <c r="AL207" s="56">
+        <v>13.2</v>
+      </c>
       <c r="AM207" s="56"/>
       <c r="AN207" s="56"/>
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v>14.285185185185181</v>
+        <v>14.228070175438592</v>
       </c>
       <c r="AR207" s="71">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31161,7 +31479,7 @@
       </c>
       <c r="AS207" s="71">
         <f t="shared" si="11"/>
-        <v>0.72440938012246114</v>
+        <v>0.66729437037587225</v>
       </c>
     </row>
     <row r="208" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31274,17 +31592,19 @@
       <c r="AK208" s="56">
         <v>14.6</v>
       </c>
-      <c r="AL208" s="56"/>
+      <c r="AL208" s="56">
+        <v>14</v>
+      </c>
       <c r="AM208" s="56"/>
       <c r="AN208" s="56"/>
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>14.180769230769227</v>
+        <v>14.174074074074072</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31407,17 +31727,19 @@
       <c r="AK209" s="56">
         <v>11</v>
       </c>
-      <c r="AL209" s="56"/>
+      <c r="AL209" s="56">
+        <v>11.25</v>
+      </c>
       <c r="AM209" s="56"/>
       <c r="AN209" s="56"/>
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.083333333333336</v>
+        <v>11.089285714285717</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31536,17 +31858,19 @@
       <c r="AK210" s="56">
         <v>15.5</v>
       </c>
-      <c r="AL210" s="56"/>
+      <c r="AL210" s="56">
+        <v>14.55</v>
+      </c>
       <c r="AM210" s="56"/>
       <c r="AN210" s="56"/>
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ210" s="71">
         <f t="shared" si="10"/>
-        <v>15.784000000000001</v>
+        <v>15.736538461538462</v>
       </c>
       <c r="AR210" s="71">
         <f>IFERROR(VLOOKUP(A210,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31554,7 +31878,7 @@
       </c>
       <c r="AS210" s="71">
         <f t="shared" si="11"/>
-        <v>1.4543297947160703</v>
+        <v>1.4068682562545316</v>
       </c>
     </row>
     <row r="211" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31665,17 +31989,19 @@
       <c r="AK211" s="56">
         <v>8.4499999999999993</v>
       </c>
-      <c r="AL211" s="56"/>
+      <c r="AL211" s="56">
+        <v>9.0500000000000007</v>
+      </c>
       <c r="AM211" s="56"/>
       <c r="AN211" s="56"/>
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ211" s="71">
         <f t="shared" si="10"/>
-        <v>8.6219999999999981</v>
+        <v>8.638461538461538</v>
       </c>
       <c r="AR211" s="71">
         <f>IFERROR(VLOOKUP(A211,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31683,7 +32009,7 @@
       </c>
       <c r="AS211" s="71">
         <f t="shared" si="11"/>
-        <v>0.54186711830959844</v>
+        <v>0.5583286567711383</v>
       </c>
     </row>
     <row r="212" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31798,17 +32124,19 @@
       <c r="AK212" s="56">
         <v>27.3</v>
       </c>
-      <c r="AL212" s="56"/>
+      <c r="AL212" s="56">
+        <v>27.75</v>
+      </c>
       <c r="AM212" s="56"/>
       <c r="AN212" s="56"/>
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v>25.679629629629616</v>
+        <v>25.753571428571416</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31820,7 +32148,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="AF1:AF212" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="K5:AO212">
     <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>""</formula>
